--- a/signup_forms/029_online_platform_user_enrollment_form--signup_forms.xlsx
+++ b/signup_forms/029_online_platform_user_enrollment_form--signup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'basic',_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Basic', 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'enterprise',_'label':_'enterprise'}</t>
+          <t>enterprise</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Enterprise', 'label': 'Enterprise'}</t>
+          <t>Enterprise</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'user',_'label':_'user'}</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'User', 'label': 'User'}</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'administrator',_'label':_'administrator'}</t>
+          <t>administrator</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Administrator', 'label': 'Administrator'}</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'moderator',_'label':_'moderator'}</t>
+          <t>moderator</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Moderator', 'label': 'Moderator'}</t>
+          <t>Moderator</t>
         </is>
       </c>
     </row>
